--- a/output_4b.xlsx
+++ b/output_4b.xlsx
@@ -449,7 +449,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>375073.02</v>
+        <v>375106.5</v>
       </c>
     </row>
     <row r="4">
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>884.17</v>
+        <v>890</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9915</v>
+        <v>9930</v>
       </c>
     </row>
     <row r="6">
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>536372.1800000001</v>
+        <v>536426.5</v>
       </c>
     </row>
     <row r="8">
@@ -499,7 +499,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>88.42</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.61</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="10">
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>888.4</v>
+        <v>889</v>
       </c>
     </row>
     <row r="11">
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10661</v>
+        <v>10662</v>
       </c>
     </row>
     <row r="12">
@@ -643,10 +643,10 @@
         <v>20000</v>
       </c>
       <c r="D3" t="n">
-        <v>15491.35</v>
+        <v>15491.7</v>
       </c>
       <c r="E3" t="n">
-        <v>35491.35</v>
+        <v>35491.7</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
@@ -665,10 +665,10 @@
         <v>26000</v>
       </c>
       <c r="D4" t="n">
-        <v>46800</v>
+        <v>46814.4</v>
       </c>
       <c r="E4" t="n">
-        <v>72800</v>
+        <v>72814.39999999999</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
@@ -709,10 +709,10 @@
         <v>12500</v>
       </c>
       <c r="D6" t="n">
-        <v>87626.67</v>
+        <v>87680.39999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>100126.67</v>
+        <v>100180.4</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
@@ -753,10 +753,10 @@
         <v>27000</v>
       </c>
       <c r="D8" t="n">
-        <v>152987</v>
+        <v>152952</v>
       </c>
       <c r="E8" t="n">
-        <v>179987</v>
+        <v>179952</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
@@ -775,16 +775,16 @@
         <v>150500</v>
       </c>
       <c r="D9" t="n">
-        <v>375073.02</v>
+        <v>375106.5</v>
       </c>
       <c r="E9" t="n">
-        <v>525573.02</v>
+        <v>525606.5</v>
       </c>
       <c r="F9" t="n">
-        <v>884.17</v>
+        <v>890</v>
       </c>
       <c r="G9" t="n">
-        <v>9915</v>
+        <v>9930</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -971,10 +971,10 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>3553</v>
+        <v>3550</v>
       </c>
       <c r="D2" t="n">
-        <v>3553.7</v>
+        <v>3554</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -983,16 +983,16 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>3553.7</v>
+        <v>3554</v>
       </c>
       <c r="H2" t="n">
-        <v>3553.7</v>
+        <v>3554</v>
       </c>
       <c r="I2" t="n">
-        <v>3553.7</v>
+        <v>3554</v>
       </c>
       <c r="J2" t="n">
-        <v>3553.7</v>
+        <v>3554</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1001,16 +1001,16 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>3553.7</v>
+        <v>3554</v>
       </c>
       <c r="N2" t="n">
-        <v>3553.7</v>
+        <v>3554</v>
       </c>
       <c r="O2" t="n">
-        <v>3553.7</v>
+        <v>3554</v>
       </c>
       <c r="P2" t="n">
-        <v>3553.7</v>
+        <v>3554</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -1019,13 +1019,13 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>2492.7</v>
+        <v>2492</v>
       </c>
       <c r="T2" t="n">
-        <v>3553.7</v>
+        <v>3554</v>
       </c>
       <c r="U2" t="n">
-        <v>3553.7</v>
+        <v>3554</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>4930</v>
+        <v>4928</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1092,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>5330.5</v>
+        <v>5331</v>
       </c>
       <c r="L3" t="n">
-        <v>5330.5</v>
+        <v>5331</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -1110,10 +1110,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5330.5</v>
+        <v>5331</v>
       </c>
       <c r="R3" t="n">
-        <v>5330.5</v>
+        <v>5331</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1125,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1869.5</v>
+        <v>1869</v>
       </c>
       <c r="W3" t="n">
-        <v>5330.5</v>
+        <v>5331</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -1180,7 +1180,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>4665</v>
+        <v>4664</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1198,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>5330.5</v>
+        <v>5328</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1216,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>5330.5</v>
+        <v>5334</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1259,13 +1259,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15000</v>
+        <v>14986</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>16327.5</v>
+        <v>16338</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>18656.8</v>
+        <v>18648</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1301,7 +1301,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>18656.8</v>
+        <v>18669</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1374,7 +1374,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1776.7</v>
+        <v>1776</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1392,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3553.7</v>
+        <v>3554</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1410,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3553.7</v>
+        <v>3554</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2600</v>
+        <v>2598</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2332.5</v>
+        <v>2334</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1492,7 +1492,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2665.2</v>
+        <v>2664</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1510,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2665.2</v>
+        <v>2667</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1571,13 +1571,13 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>866.7</v>
+        <v>866</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>777.5</v>
+        <v>778</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1595,7 +1595,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>888.4</v>
+        <v>888</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1613,7 +1613,7 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>888.4</v>
+        <v>889</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>3553</v>
+        <v>3550</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -1942,13 +1942,13 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>3553.7</v>
+        <v>3554</v>
       </c>
       <c r="L2" t="n">
-        <v>7107.3</v>
+        <v>7108</v>
       </c>
       <c r="M2" t="n">
-        <v>10661</v>
+        <v>10662</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -1960,13 +1960,13 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3553.7</v>
+        <v>3554</v>
       </c>
       <c r="R2" t="n">
-        <v>7107.3</v>
+        <v>7108</v>
       </c>
       <c r="S2" t="n">
-        <v>10661</v>
+        <v>10662</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2492.7</v>
+        <v>2492</v>
       </c>
       <c r="X2" t="n">
-        <v>6046.3</v>
+        <v>6046</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5330.5</v>
+        <v>5331</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>5330.5</v>
+        <v>5331</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -2078,7 +2078,7 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1869.5</v>
+        <v>1869</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -2124,10 +2124,10 @@
         <v>5200</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -2324,10 +2324,10 @@
         <v>4800</v>
       </c>
       <c r="I6" t="n">
-        <v>1333.3</v>
+        <v>1336</v>
       </c>
       <c r="J6" t="n">
-        <v>1333.3</v>
+        <v>1336</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -2348,22 +2348,22 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
@@ -2521,46 +2521,46 @@
         <v>603</v>
       </c>
       <c r="J8" t="n">
-        <v>1359.7</v>
+        <v>1359</v>
       </c>
       <c r="K8" t="n">
-        <v>1073.7</v>
+        <v>1073</v>
       </c>
       <c r="L8" t="n">
-        <v>1610.2</v>
+        <v>1610</v>
       </c>
       <c r="M8" t="n">
-        <v>1398.2</v>
+        <v>1398</v>
       </c>
       <c r="N8" t="n">
-        <v>1199.2</v>
+        <v>1199</v>
       </c>
       <c r="O8" t="n">
-        <v>963.2</v>
+        <v>963</v>
       </c>
       <c r="P8" t="n">
-        <v>776.2</v>
+        <v>776</v>
       </c>
       <c r="Q8" t="n">
-        <v>590.2</v>
+        <v>590</v>
       </c>
       <c r="R8" t="n">
-        <v>1285.6</v>
+        <v>1285</v>
       </c>
       <c r="S8" t="n">
-        <v>1084.6</v>
+        <v>1084</v>
       </c>
       <c r="T8" t="n">
-        <v>856.6</v>
+        <v>856</v>
       </c>
       <c r="U8" t="n">
-        <v>619.6</v>
+        <v>619</v>
       </c>
       <c r="V8" t="n">
-        <v>366.6</v>
+        <v>366</v>
       </c>
       <c r="W8" t="n">
-        <v>157.6</v>
+        <v>157</v>
       </c>
       <c r="X8" t="n">
         <v>799</v>

--- a/output_4b.xlsx
+++ b/output_4b.xlsx
@@ -8,10 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cost per Part" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Production Plan" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Inventory Plan" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Setup Decisions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Production Plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Inventory Plan" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Setup Decisions" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +438,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>150500</v>
+        <v>143000</v>
       </c>
     </row>
     <row r="3">
@@ -449,37 +448,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>375106.5</v>
+        <v>370457.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Modernization Cost X (EUR)</t>
+          <t>Backorder Cost (EUR)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>890</v>
+        <v>30750</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Modernization Cost Y (EUR)</t>
+          <t>Modernization Cost X (EUR)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9930</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Backorder Cost (EUR)</t>
+          <t>Modernization Cost Y (EUR)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>12450</v>
       </c>
     </row>
     <row r="7">
@@ -489,7 +488,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>536426.5</v>
+        <v>557677.3</v>
       </c>
     </row>
     <row r="8">
@@ -499,7 +498,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>89</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9">
@@ -509,7 +508,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.62</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -519,7 +518,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>889</v>
+        <v>902</v>
       </c>
     </row>
     <row r="11">
@@ -529,7 +528,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10662</v>
+        <v>10830</v>
       </c>
     </row>
     <row r="12">
@@ -539,7 +538,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.9333</v>
       </c>
     </row>
     <row r="13">
@@ -549,7 +548,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0.9796</v>
       </c>
     </row>
   </sheetData>
@@ -563,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:AE9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -574,37 +573,152 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Num Setups</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Setup Cost (EUR)</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Holding Cost (EUR)</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Total Cost (EUR)</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Modernization Cost X (EUR)</t>
+          <t>W5</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Modernization Cost Y (EUR)</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Backorder Cost (EUR)</t>
+          <t>W7</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>W9</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>W10</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>W11</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>W16</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>W19</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>W20</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>W21</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>W22</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>W23</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>W24</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>W25</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>W26</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>W27</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>W28</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>W29</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>W30</t>
         </is>
       </c>
     </row>
@@ -615,20 +729,95 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>32500</v>
+        <v>3602</v>
       </c>
       <c r="D2" t="n">
-        <v>33768</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>66268</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3610</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3610</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3610</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3610</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3610</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3610</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3610</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3610</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3610</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3610</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3610</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -637,20 +826,95 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>15491.7</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>35491.7</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+        <v>3500</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5409</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5415</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5409</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>5415</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2721</v>
+      </c>
+      <c r="V3" t="n">
+        <v>5415</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -659,20 +923,95 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>26000</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>46814.4</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>72814.39999999999</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3350</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>5412</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5412</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4068</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -681,20 +1020,95 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>13600</v>
       </c>
       <c r="C5" t="n">
-        <v>12500</v>
+        <v>13125</v>
       </c>
       <c r="D5" t="n">
-        <v>38400</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>50900</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>18942</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>18942</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>14238</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -703,20 +1117,95 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>12500</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>87680.39999999999</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>100180.4</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2500</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3608</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3608</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2712</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -725,20 +1214,95 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1875</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2706</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2706</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2034</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -747,47 +1311,191 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>650</v>
       </c>
       <c r="C8" t="n">
-        <v>27000</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>152952</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>179952</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>800</v>
+      </c>
+      <c r="J8" t="n">
+        <v>625</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>902</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>902</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>678</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Realized Demand E2801</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="C9" t="n">
-        <v>150500</v>
+        <v>152</v>
       </c>
       <c r="D9" t="n">
-        <v>375106.5</v>
+        <v>213</v>
       </c>
       <c r="E9" t="n">
-        <v>525606.5</v>
+        <v>106</v>
       </c>
       <c r="F9" t="n">
-        <v>890</v>
+        <v>148</v>
       </c>
       <c r="G9" t="n">
-        <v>9930</v>
+        <v>162</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>367</v>
+      </c>
+      <c r="I9" t="n">
+        <v>129</v>
+      </c>
+      <c r="J9" t="n">
+        <v>110</v>
+      </c>
+      <c r="K9" t="n">
+        <v>286</v>
+      </c>
+      <c r="L9" t="n">
+        <v>241</v>
+      </c>
+      <c r="M9" t="n">
+        <v>212</v>
+      </c>
+      <c r="N9" t="n">
+        <v>199</v>
+      </c>
+      <c r="O9" t="n">
+        <v>236</v>
+      </c>
+      <c r="P9" t="n">
+        <v>187</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>186</v>
+      </c>
+      <c r="R9" t="n">
+        <v>193</v>
+      </c>
+      <c r="S9" t="n">
+        <v>201</v>
+      </c>
+      <c r="T9" t="n">
+        <v>228</v>
+      </c>
+      <c r="U9" t="n">
+        <v>237</v>
+      </c>
+      <c r="V9" t="n">
+        <v>253</v>
+      </c>
+      <c r="W9" t="n">
+        <v>209</v>
+      </c>
+      <c r="X9" t="n">
+        <v>247</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>233</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>195</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>192</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>179</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>171</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>197</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -801,7 +1509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE9"/>
+  <dimension ref="A1:AE8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -968,70 +1676,70 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="C2" t="n">
-        <v>3550</v>
+        <v>6400</v>
       </c>
       <c r="D2" t="n">
-        <v>3554</v>
+        <v>6400</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>6400</v>
       </c>
       <c r="G2" t="n">
-        <v>3554</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>3554</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>3554</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>3554</v>
+        <v>3612</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>7222</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>10832</v>
       </c>
       <c r="M2" t="n">
-        <v>3554</v>
+        <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>3554</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>3554</v>
+        <v>10</v>
       </c>
       <c r="P2" t="n">
-        <v>3554</v>
+        <v>3620</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>7230</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>10840</v>
       </c>
       <c r="S2" t="n">
-        <v>2492</v>
+        <v>18</v>
       </c>
       <c r="T2" t="n">
-        <v>3554</v>
+        <v>18</v>
       </c>
       <c r="U2" t="n">
-        <v>3554</v>
+        <v>18</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>3628</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>7238</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -1065,19 +1773,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1200</v>
+        <v>4000</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="F3" t="n">
-        <v>4928</v>
+        <v>4000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -1092,10 +1800,10 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>5331</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>5331</v>
+        <v>5409</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -1110,10 +1818,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>5331</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>5331</v>
+        <v>5409</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1125,10 +1833,10 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1869</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>5331</v>
+        <v>2721</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -1162,25 +1870,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>5200</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>4664</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -1198,7 +1906,7 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>5328</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1216,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>5334</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1231,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>3600</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
         <v>0</v>
@@ -1259,19 +1967,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14986</v>
+        <v>3200</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="D5" t="n">
-        <v>16338</v>
+        <v>3200</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1283,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>18648</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1301,7 +2009,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>18669</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1316,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>12600</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1356,25 +2064,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="D6" t="n">
-        <v>1600</v>
+        <v>3200</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="H6" t="n">
-        <v>1776</v>
+        <v>3200</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1392,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3554</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1410,7 +2118,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3554</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1425,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1468,13 +2176,13 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2598</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2334</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1492,7 +2200,7 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2664</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1510,7 +2218,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2667</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1525,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1800</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1550,191 +2258,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>650</v>
+        <v>1230</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1728</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1515</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1409</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1261</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1099</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>732</v>
       </c>
       <c r="I8" t="n">
-        <v>866</v>
+        <v>603</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1293</v>
       </c>
       <c r="K8" t="n">
-        <v>778</v>
+        <v>1632</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1391</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1179</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>980</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>744</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>557</v>
       </c>
       <c r="Q8" t="n">
-        <v>888</v>
+        <v>1273</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>879</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>651</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>414</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="W8" t="n">
-        <v>889</v>
+        <v>854</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>607</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>600</v>
+        <v>486</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>315</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Realized Demand E2801</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>120</v>
-      </c>
-      <c r="C9" t="n">
-        <v>152</v>
-      </c>
-      <c r="D9" t="n">
-        <v>213</v>
-      </c>
-      <c r="E9" t="n">
-        <v>106</v>
-      </c>
-      <c r="F9" t="n">
-        <v>148</v>
-      </c>
-      <c r="G9" t="n">
-        <v>162</v>
-      </c>
-      <c r="H9" t="n">
-        <v>367</v>
-      </c>
-      <c r="I9" t="n">
-        <v>129</v>
-      </c>
-      <c r="J9" t="n">
-        <v>110</v>
-      </c>
-      <c r="K9" t="n">
-        <v>286</v>
-      </c>
-      <c r="L9" t="n">
-        <v>241</v>
-      </c>
-      <c r="M9" t="n">
-        <v>212</v>
-      </c>
-      <c r="N9" t="n">
-        <v>199</v>
-      </c>
-      <c r="O9" t="n">
-        <v>236</v>
-      </c>
-      <c r="P9" t="n">
-        <v>187</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>186</v>
-      </c>
-      <c r="R9" t="n">
-        <v>193</v>
-      </c>
-      <c r="S9" t="n">
-        <v>201</v>
-      </c>
-      <c r="T9" t="n">
-        <v>228</v>
-      </c>
-      <c r="U9" t="n">
-        <v>237</v>
-      </c>
-      <c r="V9" t="n">
-        <v>253</v>
-      </c>
-      <c r="W9" t="n">
-        <v>209</v>
-      </c>
-      <c r="X9" t="n">
-        <v>247</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>233</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>195</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>192</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>179</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>171</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>197</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -1915,10 +2526,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6400</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>6400</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -1927,49 +2538,49 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>3550</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>3554</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>7108</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>10662</v>
+        <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>3554</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>7108</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>10662</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1978,10 +2589,10 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2492</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>6046</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -2012,22 +2623,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -2036,16 +2647,16 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>5331</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -2054,31 +2665,31 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>5331</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1869</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
@@ -2109,25 +2720,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -2142,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -2160,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -2175,7 +2786,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -2206,19 +2817,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3200</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>3200</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -2227,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -2245,7 +2856,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -2260,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2303,31 +2914,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>4800</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>4800</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1336</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1336</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -2336,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -2348,28 +2959,28 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -2415,10 +3026,10 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -2436,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -2454,7 +3065,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -2469,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -2497,935 +3108,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1230</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>1728</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1515</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1409</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1261</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1099</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>732</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>603</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1359</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>1073</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1610</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1398</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1199</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>963</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>776</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>590</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1285</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1084</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>856</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>619</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>366</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>799</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>566</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>179</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>429</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>232</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AE8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Part</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>W13</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>W14</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>W15</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>W16</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>W17</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>W18</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>W19</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>W20</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>W21</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>W22</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>W23</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>W24</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>W25</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>W26</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>W27</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>W28</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>W29</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>W30</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>B1401</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B2302</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>B3201</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>B4702</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>V1501</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>V6302</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>E2801</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
